--- a/outputs/daily/predictions_2026-06-15.xlsx
+++ b/outputs/daily/predictions_2026-06-15.xlsx
@@ -796,12 +796,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>WC2026-012</t>
+          <t>WC2026-013</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-15T02:00:00+00:00</t>
+          <t>2026-06-15T16:00:00+00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -831,112 +831,112 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Cape Verde</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1.384998125999555</v>
+        <v>2.785258087291191</v>
       </c>
       <c r="L2" t="n">
-        <v>1.132266418144731</v>
+        <v>0.7208188971825481</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5057950242167033</v>
+        <v>0.9004212566094039</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2799777015673632</v>
+        <v>0.06992630132676335</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2142272742159335</v>
+        <v>0.02965244206383281</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4472832008078799</v>
+        <v>0.7314448167326632</v>
       </c>
       <c r="R2" t="n">
-        <v>1.560067726128229</v>
+        <v>3.056251905088653</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9099322738717717</v>
+        <v>0.7437480949113465</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4388481049862546</v>
+        <v>0.812316846473621</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2513964417489921</v>
+        <v>0.1574918422868745</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3097554532647532</v>
+        <v>0.03019131123950464</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5170265885414118</v>
+        <v>0.5858282514706551</v>
       </c>
       <c r="X2" t="n">
-        <v>0.4650808077513037</v>
+        <v>0.4354027181166962</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4140574945278053</v>
+        <v>0.7956763510078446</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.2916534112862319</v>
+        <v>0.1402575396534672</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.2942890941859628</v>
+        <v>0.06406610933868837</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4606076461532106</v>
+        <v>0.6802252690078462</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5393923538467894</v>
+        <v>0.3197747309921538</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5207058597774742</v>
+        <v>0.4879693294990406</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.4792941402225258</v>
+        <v>0.5120306705009594</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.41313</v>
+        <v>0.795365</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.29175</v>
+        <v>0.14079</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.29512</v>
+        <v>0.063845</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.46075</v>
+        <v>0.68063</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.520435</v>
+        <v>0.4887</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.384855</v>
+        <v>2.784725</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.13347</v>
+        <v>0.72024</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.518325</v>
+        <v>3.504965</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.4594292200638218</v>
+        <v>0.8433984866614899</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.2728931880606505</v>
+        <v>0.1181570502444782</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2676775918755278</v>
+        <v>0.03844446309403184</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,135 +944,135 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.4594292200638218</v>
+        <v>0.8433984866614899</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>DRAW</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>4.667939708704108</v>
+        <v>14.30077068322308</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2676775918755278</v>
+        <v>0.1181570502444782</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.05345031765959427</v>
+        <v>0.04823074891771482</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2495028602460685</v>
+        <v>0.6897368801523494</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>UNDER_2_5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4.667939708704108</v>
+        <v>3.723629489603024</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.2676775918755278</v>
+        <v>0.3197747309921538</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05345031765959427</v>
+        <v>0.05121954772481702</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.2495028602460685</v>
+        <v>0.1907226183522581</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.1164391428379744</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.1081043547555742</v>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.08393153452934991</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.07792366177554391</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.07758418501900466</v>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.07527463208858971</v>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="BE2" t="n">
-        <v>0.1391734914301297</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.09908954801397545</v>
-      </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BQ2" t="n">
+        <v>0.0662952481161812</v>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.05425937728791928</v>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="BU2" t="n">
+        <v>0.0419318555585227</v>
+      </c>
+      <c r="BV2" t="inlineStr">
         <is>
           <t>0-0</t>
         </is>
       </c>
-      <c r="BI2" t="n">
-        <v>0.09333216070581046</v>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.08761592037252035</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.07869914747531107</v>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="BO2" t="n">
-        <v>0.07738101119000149</v>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0.07162794120104066</v>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="BS2" t="n">
-        <v>0.05171699503156128</v>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="BU2" t="n">
-        <v>0.04960228216632381</v>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
       <c r="BW2" t="n">
-        <v>0.04044929517455563</v>
+        <v>0.03604597115104365</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>WC2026-013</t>
+          <t>WC2026-014</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-15T16:00:00+00:00</t>
+          <t>2026-06-15T19:00:00+00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1102,112 +1102,112 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Cape Verde</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.658174251047815</v>
+        <v>1.707850269419298</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7007389348274433</v>
+        <v>0.8922572897910839</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8813892479126065</v>
+        <v>0.601695863859714</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0813966124370582</v>
+        <v>0.23799114080638</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03721413965033527</v>
+        <v>0.160312995333906</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6977213147812059</v>
+        <v>0.4984587186077877</v>
       </c>
       <c r="R3" t="n">
-        <v>2.875202737154267</v>
+        <v>1.837631930773852</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7247972628457329</v>
+        <v>0.8323680692261476</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8121986646130412</v>
+        <v>0.5699166864478515</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1452688510223165</v>
+        <v>0.2253524438060109</v>
       </c>
       <c r="V3" t="n">
-        <v>0.04253248436464228</v>
+        <v>0.2047308697461376</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5901997576837683</v>
+        <v>0.5231305154641158</v>
       </c>
       <c r="X3" t="n">
-        <v>0.445021870851692</v>
+        <v>0.4926227089890106</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7825300275380698</v>
+        <v>0.5551522632928704</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.1497026697330186</v>
+        <v>0.2612209732814045</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.06776730272891146</v>
+        <v>0.1836267634257252</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6522310304266574</v>
+        <v>0.4815964367295193</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.3477689695733426</v>
+        <v>0.5184035632704806</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4749525865767167</v>
+        <v>0.4945974552520381</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5250474134232832</v>
+        <v>0.5054025447479619</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.78229</v>
+        <v>0.556575</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.150565</v>
+        <v>0.25928</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.067145</v>
+        <v>0.184145</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.65228</v>
+        <v>0.481435</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.475975</v>
+        <v>0.492955</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.65765</v>
+        <v>1.708575</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.701535</v>
+        <v>0.89085</v>
       </c>
       <c r="AM3" t="n">
-        <v>3.359185</v>
+        <v>2.599425</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8324577386641245</v>
+        <v>0.5789372516238512</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1208284102658887</v>
+        <v>0.2393750549750069</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.04671385106998677</v>
+        <v>0.1816876934011419</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,135 +1215,135 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.8324577386641245</v>
+        <v>0.5789372516238512</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>DRAW</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>12.28552356246119</v>
+        <v>6.237797490572501</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1208284102658887</v>
+        <v>0.1816876934011419</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.03943179782883052</v>
+        <v>0.02137469806723588</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.4844402813363033</v>
+        <v>0.1333310379655488</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>UNDER_2_5</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>3.308205470313542</v>
+        <v>6.237797490572501</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.3477689695733426</v>
+        <v>0.1816876934011419</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.04549028435454844</v>
+        <v>0.02137469806723588</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1504912075478357</v>
+        <v>0.1333310379655488</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.1244861529468182</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BG3" t="n">
+        <v>0.1155178266297448</v>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="BE3" t="n">
-        <v>0.1228641075356946</v>
-      </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BI3" t="n">
+        <v>0.1083073806593159</v>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.09663804993145245</v>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.08558265453850272</v>
+      </c>
+      <c r="BN3" t="inlineStr">
         <is>
           <t>3-0</t>
         </is>
       </c>
-      <c r="BG3" t="n">
-        <v>0.1088647356764511</v>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="BI3" t="n">
-        <v>0.0860956638430871</v>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.0859646737653473</v>
-      </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BO3" t="n">
+        <v>0.06165759641303704</v>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BM3" t="n">
-        <v>0.07628575891818751</v>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>4-0</t>
-        </is>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.07234535930556719</v>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
       <c r="BQ3" t="n">
-        <v>0.07125584802430791</v>
+        <v>0.05501443987052888</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>0-1</t>
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.05069521001949182</v>
+        <v>0.05494721735604517</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.04125448542607161</v>
+        <v>0.05048803520220289</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.03846131425777224</v>
+        <v>0.0431130022612666</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WC2026-014</t>
+          <t>WC2026-015</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T19:00:00+00:00</t>
+          <t>2026-06-15T22:00:00+00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1373,217 +1373,229 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.731541911003915</v>
+        <v>0.7844754255458772</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8887898952658139</v>
+        <v>1.851492691618772</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5889714799986413</v>
+        <v>0.1182752510749589</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2423933166919471</v>
+        <v>0.2209304192575155</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1686352033094118</v>
+        <v>0.6607943296675256</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4805884023093063</v>
+        <v>0.4556610931388</v>
       </c>
       <c r="R4" t="n">
-        <v>1.768823944703741</v>
+        <v>0.6842010492357262</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8311760552962593</v>
+        <v>1.815798950764274</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5810211382481226</v>
+        <v>0.1948915531166589</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2410150635679955</v>
+        <v>0.2729429058661605</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1779637981838819</v>
+        <v>0.5321655410171805</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4851389747323487</v>
+        <v>0.3930022632808218</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4710498519042891</v>
+        <v>0.37815482408385</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5617619948270279</v>
+        <v>0.1425937193286062</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.2584013262328181</v>
+        <v>0.241005195239851</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1798366789401539</v>
+        <v>0.6164010854315428</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4866614419649385</v>
+        <v>0.4905600175914304</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5133385580350616</v>
+        <v>0.5094399824085696</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.4958147295095119</v>
+        <v>0.46869434305272</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.5041852704904881</v>
+        <v>0.53130565694728</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.562565</v>
+        <v>0.141875</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.256575</v>
+        <v>0.240005</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.18086</v>
+        <v>0.61812</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.48699</v>
+        <v>0.49104</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.494935</v>
+        <v>0.46947</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.73168</v>
+        <v>0.78406</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.889495</v>
+        <v>1.856355</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.621175</v>
+        <v>2.640415</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.5793864890930565</v>
+        <v>0.1511705738529657</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2459129304837818</v>
+        <v>0.2441534835661251</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.1747005804231618</v>
+        <v>0.6046759425809092</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>HOME</t>
+          <t>AWAY</t>
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.5793864890930565</v>
+        <v>0.6046759425809092</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
       </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>HOME</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.454854172038353</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.1511705738529657</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.03289532277800682</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.2781251570301793</v>
+      </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>OVER_2_5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2.080782630614546</v>
+        <v>2.194613529787121</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.4866614419649385</v>
+        <v>0.4905600175914304</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006073039655632273</v>
+        <v>0.03489892445263038</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.01263667543047298</v>
+        <v>0.0765896517787612</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.1228087659074567</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.1222524080491029</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>1-1</t>
         </is>
       </c>
-      <c r="BE4" t="n">
-        <v>0.1232055014926901</v>
-      </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BI4" t="n">
+        <v>0.1144746671324568</v>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.09634045889601608</v>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.08205664998688576</v>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.07579317751479223</v>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="BQ4" t="n">
+        <v>0.05945788518439085</v>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>1-0</t>
         </is>
       </c>
-      <c r="BG4" t="n">
-        <v>0.1148191609265964</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="BI4" t="n">
-        <v>0.1091041623699363</v>
-      </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BS4" t="n">
+        <v>0.04580076811320281</v>
+      </c>
+      <c r="BT4" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BK4" t="n">
-        <v>0.09697067704584007</v>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.0839793686467314</v>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>3-0</t>
-        </is>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.06297280993617367</v>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="BQ4" t="n">
-        <v>0.0559695971477658</v>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0-1</t>
-        </is>
-      </c>
-      <c r="BS4" t="n">
-        <v>0.05348462278578574</v>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
       <c r="BU4" t="n">
-        <v>0.04977445671266367</v>
+        <v>0.0408193469149803</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1591,18 +1603,18 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.04309327894771363</v>
+        <v>0.03778836124486865</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>WC2026-015</t>
+          <t>WC2026-016</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-15T22:00:00+00:00</t>
+          <t>2026-06-16T01:00:00+00:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1612,7 +1624,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1632,229 +1644,193 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.79848898536543</v>
+        <v>1.89018461394325</v>
       </c>
       <c r="L5" t="n">
-        <v>1.810329340983212</v>
+        <v>0.8815477774703798</v>
       </c>
       <c r="M5" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.1264281937632137</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.2238010135569816</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.6497707926798046</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.4716676007605239</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.7190342555148798</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.84096574448512</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="n">
-        <v>0.1743142107408941</v>
+        <v>0.6038413363809759</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2379271699125768</v>
+        <v>0.2326876471702652</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5877586193465292</v>
+        <v>0.1634710164487588</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4184072750149574</v>
+        <v>0.4148881940066993</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4153398154346803</v>
+        <v>0.449358759486398</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1500283407431322</v>
+        <v>0.6004445459883783</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.2465563134017592</v>
+        <v>0.2399882506526304</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.603415345855109</v>
+        <v>0.159567203358991</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4837802566711448</v>
+        <v>0.5237786109983932</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5162197433288551</v>
+        <v>0.4762213890016068</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4706547521213347</v>
+        <v>0.5077910419205115</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.5293452478786653</v>
+        <v>0.4922089580794885</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1495</v>
+        <v>0.60255</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.24584</v>
+        <v>0.237695</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.60466</v>
+        <v>0.159755</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.483995</v>
+        <v>0.524075</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.471555</v>
+        <v>0.50706</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.79841</v>
+        <v>1.89131</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.813275</v>
+        <v>0.88015</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.611685</v>
+        <v>2.77146</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.1490883364503815</v>
+        <v>0.6023127807043072</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.2344339932426343</v>
+        <v>0.2359729187373296</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.6164776703069843</v>
+        <v>0.1617143005583633</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>AWAY</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="AR5" t="n">
-        <v>0.6164776703069843</v>
+        <v>0.6023127807043072</v>
       </c>
       <c r="AS5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.909628147285654</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.1490883364503815</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.02266014268716773</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0.1792333024199311</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>HOME</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>7.909628147285654</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0.1490883364503815</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0.02266014268716773</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0.1792333024199311</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
       <c r="BD5" t="inlineStr">
         <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.1146560096379492</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.1117461350120859</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.1078150552748751</v>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.09850955696080935</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.072977125754251</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.07040694168915664</v>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.06206708296456267</v>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.04594306839543481</v>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
           <t>0-1</t>
         </is>
       </c>
-      <c r="BE5" t="n">
-        <v>0.1226373532641892</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="BG5" t="n">
-        <v>0.120639968023503</v>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="BI5" t="n">
-        <v>0.1170645051471305</v>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.09632968566160482</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.08426395942647046</v>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0-3</t>
-        </is>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.07279935793607466</v>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>1-3</t>
-        </is>
-      </c>
-      <c r="BQ5" t="n">
-        <v>0.05812948545363101</v>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BS5" t="n">
-        <v>0.04814391409400989</v>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
       <c r="BU5" t="n">
-        <v>0.04248850815329017</v>
+        <v>0.0447209357322995</v>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
@@ -1862,7 +1838,7 @@
         </is>
       </c>
       <c r="BW5" t="n">
-        <v>0.03845909648225282</v>
+        <v>0.04342044049919663</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/daily/predictions_2026-06-15.xlsx
+++ b/outputs/daily/predictions_2026-06-15.xlsx
@@ -843,31 +843,31 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2.785258087291191</v>
+        <v>2.487239718175314</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7208188971825481</v>
+        <v>0.677837266298426</v>
       </c>
       <c r="M2" t="b">
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9004212566094039</v>
+        <v>0.8416567148688127</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06992630132676335</v>
+        <v>0.1114438219717493</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02965244206383281</v>
+        <v>0.04689946315943798</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.7314448167326632</v>
+        <v>0.61646106705934</v>
       </c>
       <c r="R2" t="n">
-        <v>3.056251905088653</v>
+        <v>2.514400324877966</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7437480949113465</v>
+        <v>0.6655996751220337</v>
       </c>
       <c r="T2" t="n">
         <v>0.812316846473621</v>
@@ -885,58 +885,58 @@
         <v>0.4354027181166962</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7956763510078446</v>
+        <v>0.7623902671245554</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.1402575396534672</v>
+        <v>0.1638667400061782</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.06406610933868837</v>
+        <v>0.07374299286926671</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.6802252690078462</v>
+        <v>0.61273727785819</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3197747309921538</v>
+        <v>0.38726272214181</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.4879693294990406</v>
+        <v>0.4584724252790171</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5120306705009594</v>
+        <v>0.5415275747209829</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.795365</v>
+        <v>0.762705</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.14079</v>
+        <v>0.163585</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.063845</v>
+        <v>0.07371</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.68063</v>
+        <v>0.61326</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.4887</v>
+        <v>0.458405</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.784725</v>
+        <v>2.487615</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.72024</v>
+        <v>0.67645</v>
       </c>
       <c r="AM2" t="n">
-        <v>3.504965</v>
+        <v>3.164065</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8433984866614899</v>
+        <v>0.8115711489944311</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.1181570502444782</v>
+        <v>0.1406663585906503</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.03844446309403184</v>
+        <v>0.04776249241491848</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         </is>
       </c>
       <c r="AR2" t="n">
-        <v>0.8433984866614899</v>
+        <v>0.8115711489944311</v>
       </c>
       <c r="AS2" t="b">
         <v>1</v>
@@ -955,33 +955,33 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>14.30077068322308</v>
+        <v>8.973130877129257</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.1181570502444782</v>
+        <v>0.1406663585906503</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.04823074891771482</v>
+        <v>0.02922253661890098</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.6897368801523494</v>
+        <v>0.2622176456431009</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>UNDER_2_5</t>
+          <t>DRAW</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>3.723629489603024</v>
+        <v>8.973130877129257</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.3197747309921538</v>
+        <v>0.1406663585906503</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.05121954772481702</v>
+        <v>0.02922253661890098</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.1907226183522581</v>
+        <v>0.2622176456431009</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="BE2" t="n">
-        <v>0.1164391428379744</v>
+        <v>0.1305736113705813</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -997,71 +997,71 @@
         </is>
       </c>
       <c r="BG2" t="n">
-        <v>0.1081043547555742</v>
+        <v>0.1082559574488326</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="BI2" t="n">
+        <v>0.09787785592428924</v>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="BI2" t="n">
-        <v>0.08393153452934991</v>
-      </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="n">
+        <v>0.08850765978214795</v>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.07828632282519733</v>
+      </c>
+      <c r="BN2" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="BK2" t="n">
-        <v>0.07792366177554391</v>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>1-0</t>
-        </is>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.07758418501900466</v>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="n">
+        <v>0.07337992225763539</v>
+      </c>
+      <c r="BP2" t="inlineStr">
         <is>
           <t>4-0</t>
         </is>
       </c>
-      <c r="BO2" t="n">
-        <v>0.07527463208858971</v>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
       <c r="BQ2" t="n">
-        <v>0.0662952481161812</v>
+        <v>0.06731462927395827</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="BS2" t="n">
+        <v>0.04933031803198508</v>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
           <t>4-1</t>
         </is>
       </c>
-      <c r="BS2" t="n">
-        <v>0.05425937728791928</v>
-      </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="n">
+        <v>0.04562836428895187</v>
+      </c>
+      <c r="BV2" t="inlineStr">
         <is>
           <t>5-0</t>
         </is>
       </c>
-      <c r="BU2" t="n">
-        <v>0.0419318555585227</v>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0-0</t>
-        </is>
-      </c>
       <c r="BW2" t="n">
-        <v>0.03604597115104365</v>
+        <v>0.03348552390888713</v>
       </c>
     </row>
     <row r="3">
@@ -1114,31 +1114,31 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1.707850269419298</v>
+        <v>1.709248948001816</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8922572897910839</v>
+        <v>0.896358611208566</v>
       </c>
       <c r="M3" t="b">
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.601695863859714</v>
+        <v>0.6021916612300341</v>
       </c>
       <c r="O3" t="n">
-        <v>0.23799114080638</v>
+        <v>0.234949669396024</v>
       </c>
       <c r="P3" t="n">
-        <v>0.160312995333906</v>
+        <v>0.162858669373942</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4984587186077877</v>
+        <v>0.5009728614460659</v>
       </c>
       <c r="R3" t="n">
-        <v>1.837631930773852</v>
+        <v>1.840174982742067</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8323680692261476</v>
+        <v>0.8398250172579332</v>
       </c>
       <c r="T3" t="n">
         <v>0.5699166864478515</v>
@@ -1156,58 +1156,58 @@
         <v>0.4926227089890106</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5551522632928704</v>
+        <v>0.5544566506727574</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.2612209732814045</v>
+        <v>0.2611211013898802</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1836267634257252</v>
+        <v>0.1844222479373625</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.4815964367295193</v>
+        <v>0.482976265151982</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5184035632704806</v>
+        <v>0.517023734848018</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.4945974552520381</v>
+        <v>0.4961193679233392</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.5054025447479619</v>
+        <v>0.5038806320766609</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.556575</v>
+        <v>0.55582</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.25928</v>
+        <v>0.259235</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.184145</v>
+        <v>0.184945</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.481435</v>
+        <v>0.48297</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.492955</v>
+        <v>0.494515</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.708575</v>
+        <v>1.709985</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.89085</v>
+        <v>0.895095</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.599425</v>
+        <v>2.60508</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.5789372516238512</v>
+        <v>0.578961667416951</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.2393750549750069</v>
+        <v>0.2381334984379835</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.1816876934011419</v>
+        <v>0.1829048341450656</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="AR3" t="n">
-        <v>0.5789372516238512</v>
+        <v>0.578961667416951</v>
       </c>
       <c r="AS3" t="b">
         <v>1</v>
@@ -1226,16 +1226,16 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>6.237797490572501</v>
+        <v>6.140293322082145</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.1816876934011419</v>
+        <v>0.1829048341450656</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02137469806723588</v>
+        <v>0.02004616477112359</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.1333310379655488</v>
+        <v>0.1230893316774884</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>6.237797490572501</v>
+        <v>6.140293322082145</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.1816876934011419</v>
+        <v>0.1829048341450656</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.02137469806723588</v>
+        <v>0.02004616477112359</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.1333310379655488</v>
+        <v>0.1230893316774884</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="BE3" t="n">
-        <v>0.1244861529468182</v>
+        <v>0.1244742882646981</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         </is>
       </c>
       <c r="BG3" t="n">
-        <v>0.1155178266297448</v>
+        <v>0.1149265350149212</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="BI3" t="n">
-        <v>0.1083073806593159</v>
+        <v>0.1078898270935881</v>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>0.09663804993145245</v>
+        <v>0.09670797557714091</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>0.08558265453850272</v>
+        <v>0.08517423672440638</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>0.06165759641303704</v>
+        <v>0.06147019115327104</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="BQ3" t="n">
-        <v>0.05501443987052888</v>
+        <v>0.05509933517287111</v>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="BS3" t="n">
-        <v>0.05494721735604517</v>
+        <v>0.05488776159332786</v>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="BU3" t="n">
-        <v>0.05048803520220289</v>
+        <v>0.05071527280005431</v>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.0431130022612666</v>
+        <v>0.04334251334055898</v>
       </c>
     </row>
     <row r="4">
@@ -1385,31 +1385,31 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7844754255458772</v>
+        <v>0.7817987100960617</v>
       </c>
       <c r="L4" t="n">
-        <v>1.851492691618772</v>
+        <v>1.865169407068588</v>
       </c>
       <c r="M4" t="b">
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1182752510749589</v>
+        <v>0.1138967428690478</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2209304192575155</v>
+        <v>0.21722190378795</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6607943296675256</v>
+        <v>0.6688813533430021</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4556610931388</v>
+        <v>0.4607835970215209</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6842010492357262</v>
+        <v>0.6793342938724254</v>
       </c>
       <c r="S4" t="n">
-        <v>1.815798950764274</v>
+        <v>1.840665706127575</v>
       </c>
       <c r="T4" t="n">
         <v>0.1948915531166589</v>
@@ -1427,58 +1427,58 @@
         <v>0.37815482408385</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1425937193286062</v>
+        <v>0.1406088653006088</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.241005195239851</v>
+        <v>0.2392334918271715</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.6164010854315428</v>
+        <v>0.6201576428722199</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.4905600175914304</v>
+        <v>0.4932943823303478</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5094399824085696</v>
+        <v>0.5067056176696523</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.46869434305272</v>
+        <v>0.468746789635361</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.53130565694728</v>
+        <v>0.531253210364639</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.141875</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.240005</v>
+        <v>0.23835</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.61812</v>
+        <v>0.62165</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.49104</v>
+        <v>0.493695</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.46947</v>
+        <v>0.469435</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.78406</v>
+        <v>0.781515</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.856355</v>
+        <v>1.86857</v>
       </c>
       <c r="AM4" t="n">
-        <v>2.640415</v>
+        <v>2.650085</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.1511705738529657</v>
+        <v>0.148922957063602</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.2441534835661251</v>
+        <v>0.2422271515251291</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6046759425809092</v>
+        <v>0.608849891411269</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         </is>
       </c>
       <c r="AR4" t="n">
-        <v>0.6046759425809092</v>
+        <v>0.608849891411269</v>
       </c>
       <c r="AS4" t="b">
         <v>1</v>
@@ -1497,33 +1497,33 @@
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>8.454854172038353</v>
+        <v>8.779882328590771</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1511705738529657</v>
+        <v>0.148922957063602</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.03289532277800682</v>
+        <v>0.03502621419455412</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.2781251570301793</v>
+        <v>0.3075260390442009</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>OVER_2_5</t>
+          <t>HOME</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>2.194613529787121</v>
+        <v>8.779882328590771</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.4905600175914304</v>
+        <v>0.148922957063602</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.03489892445263038</v>
+        <v>0.03502621419455412</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0765896517787612</v>
+        <v>0.3075260390442009</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         </is>
       </c>
       <c r="BE4" t="n">
-        <v>0.1228087659074567</v>
+        <v>0.1232664293421091</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="BG4" t="n">
-        <v>0.1222524080491029</v>
+        <v>0.1218435980835813</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="BI4" t="n">
-        <v>0.1144746671324568</v>
+        <v>0.1136695558074751</v>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>0.09634045889601608</v>
+        <v>0.09636953545780824</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
@@ -1563,7 +1563,7 @@
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>0.08205664998688576</v>
+        <v>0.08119964898827622</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>0.07579317751479223</v>
+        <v>0.0766375909758279</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         </is>
       </c>
       <c r="BQ4" t="n">
-        <v>0.05945788518439085</v>
+        <v>0.05991516976977183</v>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="BS4" t="n">
-        <v>0.04580076811320281</v>
+        <v>0.04506939284701902</v>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="BU4" t="n">
-        <v>0.0408193469149803</v>
+        <v>0.04039396004885289</v>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
         </is>
       </c>
       <c r="BW4" t="n">
-        <v>0.03778836124486865</v>
+        <v>0.03767078925673559</v>
       </c>
     </row>
     <row r="5">
